--- a/samples/sample_profiling.xlsx
+++ b/samples/sample_profiling.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lengkap</t>
+          <t>-</t>
         </is>
       </c>
     </row>
